--- a/MakerPnPControl-core_variant1_cpl.xlsx
+++ b/MakerPnPControl-core_variant1_cpl.xlsx
@@ -8,15 +8,28 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\Hydra\Documents\DipTrace\Projects\MakerPnPControl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{E7313F6C-DD4A-45C4-B487-D08E1FB390E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DDE2440-27A9-41F0-8E58-604B7BB312D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17235" yWindow="2700" windowWidth="23325" windowHeight="16140" xr2:uid="{5C73AB7E-0ECA-4E12-BEC9-2B5752DC5265}"/>
+    <workbookView xWindow="29865" yWindow="8985" windowWidth="25155" windowHeight="21300" xr2:uid="{5C73AB7E-0ECA-4E12-BEC9-2B5752DC5265}"/>
   </bookViews>
   <sheets>
     <sheet name="MakerPnPControl-core_variant1_c" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
